--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484799_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484799_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4786</v>
+        <v>8.7674</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8278</v>
+        <v>6.9146</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6508</v>
+        <v>1.8528</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6296</v>
+        <v>8.6417</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8538</v>
+        <v>1.9315</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7758</v>
+        <v>6.7102</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6468</v>
+        <v>7.199</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0839</v>
+        <v>1.4634</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5629</v>
+        <v>5.7356</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9828</v>
+        <v>1.4426</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.23</v>
+        <v>0.468</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2129</v>
+        <v>0.9746</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R2" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>1.415</v>
+        <v>-1.6099</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0305</v>
+        <v>-0.2462</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3846</v>
+        <v>-1.3637</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4904</v>
+        <v>1.547</v>
       </c>
       <c r="W2" t="n">
-        <v>3.094</v>
+        <v>1.8488</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.3828</v>
+        <v>6.947</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9533</v>
+        <v>4.3809</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4296</v>
+        <v>2.5661</v>
       </c>
       <c r="G3" t="n">
-        <v>8.6417</v>
+        <v>3.6296</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9315</v>
+        <v>0.8538</v>
       </c>
       <c r="I3" t="n">
-        <v>6.7102</v>
+        <v>2.7758</v>
       </c>
       <c r="J3" t="n">
-        <v>7.199</v>
+        <v>2.6468</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4634</v>
+        <v>1.0839</v>
       </c>
       <c r="L3" t="n">
-        <v>5.7356</v>
+        <v>1.5629</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4426</v>
+        <v>0.9828</v>
       </c>
       <c r="N3" t="n">
-        <v>0.468</v>
+        <v>-0.23</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9746</v>
+        <v>1.2129</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9946</v>
+        <v>-0.1165</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2076</v>
+        <v>-0.4164</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.787</v>
+        <v>0.2999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.547</v>
+        <v>2.4904</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8488</v>
+        <v>3.094</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3879</v>
+        <v>3.2602</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2273</v>
+        <v>0.9938</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1606</v>
+        <v>2.2664</v>
       </c>
       <c r="G4" t="n">
         <v>2.009</v>
@@ -766,13 +766,13 @@
         <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.074</v>
+        <v>-1.2017</v>
       </c>
       <c r="T4" t="n">
-        <v>0.074</v>
+        <v>-0.1595</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.148</v>
+        <v>-1.0422</v>
       </c>
       <c r="V4" t="n">
         <v>1.8868</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5018</v>
+        <v>2.3025</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8881</v>
+        <v>2.3499</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6138</v>
+        <v>-0.0474</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9432</v>
+        <v>1.6992</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4125</v>
+        <v>-0.576</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5306999999999999</v>
+        <v>2.2752</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3383</v>
+        <v>2.0576</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5439000000000001</v>
+        <v>0.0423</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2057</v>
+        <v>2.0154</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2814</v>
+        <v>-0.3584</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9564</v>
+        <v>-0.6182</v>
       </c>
       <c r="O5" t="n">
-        <v>0.325</v>
+        <v>0.2598</v>
       </c>
       <c r="P5" t="n">
-        <v>1.887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.887</v>
+        <v>0.3774</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9699</v>
+        <v>0.2259</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0189</v>
+        <v>0.2923</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.951</v>
+        <v>-0.0664</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1689</v>
+        <v>2.0567</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0576</v>
+        <v>0.6545</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1113</v>
+        <v>1.4021</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6992</v>
+        <v>0.9432</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.576</v>
+        <v>0.4125</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2752</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0576</v>
+        <v>-0.3383</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0423</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0154</v>
+        <v>0.2057</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3584</v>
+        <v>1.2814</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6182</v>
+        <v>0.9564</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2598</v>
+        <v>0.325</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09229999999999999</v>
+        <v>-1.4151</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.2524</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09229999999999999</v>
+        <v>-1.1627</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3815</v>
+        <v>0.4609</v>
       </c>
       <c r="E8" t="n">
         <v>0.3841</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0026</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.2278</v>
@@ -1078,13 +1078,13 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3368</v>
+        <v>-0.2575</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3368</v>
+        <v>-0.2575</v>
       </c>
       <c r="V8" t="n">
         <v>0.3018</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.224</v>
+        <v>-0.0031</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8542</v>
+        <v>-0.5804</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6303</v>
+        <v>0.5774</v>
       </c>
       <c r="G9" t="n">
         <v>4.6665</v>
@@ -1156,13 +1156,13 @@
         <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8147</v>
+        <v>-0.5939</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7396</v>
+        <v>-0.4658</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0752</v>
+        <v>-0.1281</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2452</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1938</v>
+        <v>-1.2349</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1164</v>
+        <v>-0.9988</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0774</v>
+        <v>-0.2361</v>
       </c>
       <c r="G10" t="n">
         <v>0.1377</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1428</v>
+        <v>-0.184</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2352</v>
+        <v>-0.1176</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.0664</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6226</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4312</v>
+        <v>-2.6896</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5161</v>
+        <v>-5.1448</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0849</v>
+        <v>2.4552</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0655</v>
@@ -1312,13 +1312,13 @@
         <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4978</v>
+        <v>-0.7562</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8107</v>
+        <v>-0.4395</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6872</v>
+        <v>-0.3168</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9058</v>
+        <v>-2.9105</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1464</v>
+        <v>-4.5215</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2406</v>
+        <v>1.611</v>
       </c>
       <c r="G12" t="n">
         <v>0.8935</v>
@@ -1390,13 +1390,13 @@
         <v>2.0757</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.4218</v>
+        <v>-2.4266</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0923</v>
+        <v>-0.4674</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3296</v>
+        <v>-1.9592</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6226</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0748</v>
+        <v>-3.3088</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7991</v>
+        <v>-4.3505</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7243000000000001</v>
+        <v>1.0417</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0662</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0651</v>
+        <v>-1.2991</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.622</v>
+        <v>-0.1735</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4431</v>
+        <v>-1.1257</v>
       </c>
       <c r="V13" t="n">
         <v>1.2452</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.3397</v>
+        <v>15.5156</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7738000000000023</v>
+        <v>1.9496</v>
       </c>
       <c r="F14" t="n">
-        <v>13.5662</v>
+        <v>13.566</v>
       </c>
       <c r="G14" t="n">
         <v>18.5843</v>
       </c>
       <c r="H14" t="n">
-        <v>2.997499999999999</v>
+        <v>2.9975</v>
       </c>
       <c r="I14" t="n">
         <v>15.5869</v>
@@ -1522,10 +1522,10 @@
         <v>10.2092</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5790000000000004</v>
+        <v>0.579</v>
       </c>
       <c r="L14" t="n">
-        <v>9.6303</v>
+        <v>9.630300000000002</v>
       </c>
       <c r="M14" t="n">
         <v>8.375</v>
@@ -1546,13 +1546,13 @@
         <v>15.096</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.8102</v>
+        <v>-9.634599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.6218</v>
+        <v>-2.446</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.1887</v>
+        <v>-7.1888</v>
       </c>
       <c r="V14" t="n">
         <v>5.622399999999999</v>
@@ -1561,7 +1561,7 @@
         <v>8.338600000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.7162</v>
+        <v>-2.716200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8251</v>
+        <v>6.6046</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6669</v>
+        <v>5.0567</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1582</v>
+        <v>1.5479</v>
       </c>
       <c r="G15" t="n">
         <v>4.0186</v>
@@ -1624,13 +1624,13 @@
         <v>2.2644</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8064</v>
+        <v>2.5859</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1409</v>
+        <v>1.5306</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6655</v>
+        <v>1.0553</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9434</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8919</v>
+        <v>2.5315</v>
       </c>
       <c r="E16" t="n">
-        <v>3.41</v>
+        <v>1.9485</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4819</v>
+        <v>0.583</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8393</v>
@@ -1702,13 +1702,13 @@
         <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>4.0144</v>
+        <v>2.6539</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3835</v>
+        <v>1.922</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6308</v>
+        <v>0.7319</v>
       </c>
       <c r="V16" t="n">
         <v>-0.038</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8522</v>
+        <v>-0.0151</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7763</v>
+        <v>-2.3865</v>
       </c>
       <c r="F17" t="n">
-        <v>1.924</v>
+        <v>2.3714</v>
       </c>
       <c r="G17" t="n">
         <v>-2.4463</v>
@@ -1780,13 +1780,13 @@
         <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1041</v>
+        <v>0.733</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.291</v>
+        <v>0.0987</v>
       </c>
       <c r="U17" t="n">
-        <v>0.187</v>
+        <v>0.6343</v>
       </c>
       <c r="V17" t="n">
         <v>0.9434</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0788</v>
+        <v>-1.5408</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.5538</v>
+        <v>-0.2466</v>
       </c>
       <c r="F18" t="n">
-        <v>2.475</v>
+        <v>-1.2942</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.2641</v>
+        <v>-2.5448</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.2987</v>
+        <v>1.0988</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0346</v>
+        <v>-3.6435</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.6112</v>
+        <v>0.0221</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.0609</v>
+        <v>1.9126</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5503</v>
+        <v>-1.8905</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3471</v>
+        <v>-2.5669</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7623</v>
+        <v>-0.8139</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5849</v>
+        <v>-1.753</v>
       </c>
       <c r="P18" t="n">
         <v>-0.3774</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1322</v>
+        <v>-3.0192</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1097</v>
+        <v>1.3624</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1896</v>
+        <v>0.8827</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>0.4797</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.547</v>
+        <v>0.019</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.547</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8891</v>
+        <v>-2.0649</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1235</v>
+        <v>-4.1384</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7656</v>
+        <v>2.0734</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5448</v>
+        <v>-3.2641</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0988</v>
+        <v>-3.2987</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.6435</v>
+        <v>0.0346</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0221</v>
+        <v>-4.6112</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9126</v>
+        <v>-4.0609</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8905</v>
+        <v>-0.5503</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5669</v>
+        <v>1.3471</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8139</v>
+        <v>0.7623</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.753</v>
+        <v>0.5849</v>
       </c>
       <c r="P19" t="n">
         <v>-0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0192</v>
+        <v>-1.1322</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6418</v>
+        <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0141</v>
+        <v>3.1235</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0058</v>
+        <v>1.605</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0083</v>
+        <v>1.5185</v>
       </c>
       <c r="V19" t="n">
-        <v>0.019</v>
+        <v>-1.547</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8678</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8488</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9656</v>
+        <v>-3.6672</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5378</v>
+        <v>-2.3429</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4278</v>
+        <v>-1.3243</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6541</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0658</v>
+        <v>0.3642</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0436</v>
+        <v>0.1513</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1094</v>
+        <v>0.2128</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1886</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1111</v>
+        <v>-3.7719</v>
       </c>
       <c r="E21" t="n">
         <v>-2.33</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7811</v>
+        <v>-1.4419</v>
       </c>
       <c r="G21" t="n">
         <v>-4.9827</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3621</v>
+        <v>0.7013</v>
       </c>
       <c r="T21" t="n">
         <v>0.2751</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.4262</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6226</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1731</v>
+        <v>-4.6363</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0801</v>
+        <v>-4.3647</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.093</v>
+        <v>-0.2716</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7599</v>
+        <v>-3.1116</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7014</v>
+        <v>-0.3905</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0585</v>
+        <v>-2.7211</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7822</v>
+        <v>-1.4444</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8233</v>
+        <v>-0.8445</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0411</v>
+        <v>-0.5999</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.9777</v>
+        <v>-1.6673</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8781</v>
+        <v>0.4539</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0996</v>
+        <v>-2.1212</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0757</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9627</v>
+        <v>-3.0192</v>
       </c>
       <c r="R22" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6625</v>
+        <v>1.2302</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.7405</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0023</v>
+        <v>0.4897</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.987</v>
+        <v>-5.7336</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2416</v>
+        <v>-4.6647</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7454</v>
+        <v>-1.0689</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1116</v>
+        <v>-3.7599</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3905</v>
+        <v>-1.7014</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7211</v>
+        <v>-2.0585</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4444</v>
+        <v>-0.7822</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8445</v>
+        <v>-0.8233</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5999</v>
+        <v>0.0411</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6673</v>
+        <v>-2.9777</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4539</v>
+        <v>-0.8781</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1212</v>
+        <v>-2.0996</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5096</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0192</v>
+        <v>-3.9627</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1206</v>
+        <v>0.102</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1365</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0159</v>
+        <v>0.0218</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.3399</v>
+        <v>-12.2937</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.5662</v>
+        <v>-13.4686</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7738000000000004</v>
+        <v>1.1748</v>
       </c>
       <c r="G24" t="n">
         <v>-18.5842</v>
@@ -2299,13 +2299,13 @@
         <v>-15.5868</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.375</v>
+        <v>-8.375000000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.418500000000001</v>
+        <v>-2.4185</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.9566</v>
+        <v>-5.956599999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-10.2094</v>
@@ -2314,7 +2314,7 @@
         <v>-0.579</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.630199999999999</v>
+        <v>-9.6302</v>
       </c>
       <c r="P24" t="n">
         <v>-0.9434999999999996</v>
@@ -2326,16 +2326,16 @@
         <v>14.1525</v>
       </c>
       <c r="S24" t="n">
-        <v>10.8103</v>
+        <v>12.8564</v>
       </c>
       <c r="T24" t="n">
-        <v>7.1886</v>
+        <v>7.286099999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>3.621599999999999</v>
+        <v>5.5702</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.622400000000001</v>
+        <v>-5.6224</v>
       </c>
       <c r="W24" t="n">
         <v>2.7162</v>
